--- a/output/Tables/Sensitivity analyses/HIA_age_sensitivity_1000replicate.xlsx
+++ b/output/Tables/Sensitivity analyses/HIA_age_sensitivity_1000replicate.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -390,6 +390,36 @@
           <t>tot_daly_up</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -398,22 +428,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>27034.358</v>
+        <v>24665.324</v>
       </c>
       <c r="C2">
-        <v>25907.74</v>
+        <v>23583.938</v>
       </c>
       <c r="D2">
-        <v>28161.718</v>
+        <v>25745.921</v>
       </c>
       <c r="E2">
-        <v>540949.474</v>
+        <v>498311.378</v>
       </c>
       <c r="F2">
-        <v>523985.041</v>
+        <v>481785.715</v>
       </c>
       <c r="G2">
-        <v>558003.976</v>
+        <v>514865.862</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>66275960904.076</v>
+      </c>
+      <c r="L2">
+        <v>64066474703.742</v>
+      </c>
+      <c r="M2">
+        <v>68473414556.239</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>26305.826</v>
+        <v>23394.631</v>
       </c>
       <c r="C3">
-        <v>25017.574</v>
+        <v>22155.305</v>
       </c>
       <c r="D3">
-        <v>27594.333</v>
+        <v>24640.311</v>
       </c>
       <c r="E3">
-        <v>33314.251</v>
+        <v>35308.979</v>
       </c>
       <c r="F3">
-        <v>31928.425</v>
+        <v>33635.354</v>
       </c>
       <c r="G3">
-        <v>34699.806</v>
+        <v>36993.283</v>
+      </c>
+      <c r="H3">
+        <v>1232763784.807</v>
+      </c>
+      <c r="I3">
+        <v>1167612264.332</v>
+      </c>
+      <c r="J3">
+        <v>1298477649.283</v>
+      </c>
+      <c r="K3">
+        <v>4696400769.087</v>
+      </c>
+      <c r="L3">
+        <v>4473434257.746</v>
+      </c>
+      <c r="M3">
+        <v>4920011144.192</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>6127.938</v>
+        <v>5502.754</v>
       </c>
       <c r="C4">
-        <v>5854.019</v>
+        <v>5238.087</v>
       </c>
       <c r="D4">
-        <v>6405.614</v>
+        <v>5771.632</v>
       </c>
       <c r="E4">
-        <v>12378.516</v>
+        <v>8380.208000000001</v>
       </c>
       <c r="F4">
-        <v>11821.05</v>
+        <v>7920.621</v>
       </c>
       <c r="G4">
-        <v>12950.119</v>
+        <v>8855.288</v>
+      </c>
+      <c r="H4">
+        <v>215740632.682</v>
+      </c>
+      <c r="I4">
+        <v>205340431.624</v>
+      </c>
+      <c r="J4">
+        <v>226319633.746</v>
+      </c>
+      <c r="K4">
+        <v>1114480913.277</v>
+      </c>
+      <c r="L4">
+        <v>1053250376.173</v>
+      </c>
+      <c r="M4">
+        <v>1177343243.448</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>5521.052</v>
+        <v>4808.079</v>
       </c>
       <c r="C5">
-        <v>5167.9</v>
+        <v>4478.69</v>
       </c>
       <c r="D5">
-        <v>5877.186</v>
+        <v>5140.857</v>
       </c>
       <c r="E5">
-        <v>18421.697</v>
+        <v>5369.319</v>
       </c>
       <c r="F5">
-        <v>17400.563</v>
+        <v>5002.827</v>
       </c>
       <c r="G5">
-        <v>19451.814</v>
+        <v>5740.461</v>
+      </c>
+      <c r="H5">
+        <v>80032866.352</v>
+      </c>
+      <c r="I5">
+        <v>74577815.523</v>
+      </c>
+      <c r="J5">
+        <v>85578016.508</v>
+      </c>
+      <c r="K5">
+        <v>714014215.553</v>
+      </c>
+      <c r="L5">
+        <v>665406043.044</v>
+      </c>
+      <c r="M5">
+        <v>763509514.286</v>
       </c>
     </row>
     <row r="6">
@@ -498,47 +600,83 @@
         </is>
       </c>
       <c r="B6">
-        <v>128601.72</v>
+        <v>114266.667</v>
       </c>
       <c r="C6">
-        <v>123394.59</v>
+        <v>109462.168</v>
       </c>
       <c r="D6">
-        <v>133826.081</v>
+        <v>119086.433</v>
       </c>
       <c r="E6">
-        <v>45500.044</v>
+        <v>47135.932</v>
       </c>
       <c r="F6">
-        <v>43150.962</v>
+        <v>44735.272</v>
       </c>
       <c r="G6">
-        <v>47913.614</v>
+        <v>49543.918</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>6267991809.632</v>
+      </c>
+      <c r="L6">
+        <v>5951295360.867</v>
+      </c>
+      <c r="M6">
+        <v>6587921141.255</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>Chronic diseases</t>
         </is>
       </c>
       <c r="B7">
-        <v>166556.536</v>
+        <v>147972.131</v>
       </c>
       <c r="C7">
-        <v>159434.083</v>
+        <v>141334.25</v>
       </c>
       <c r="D7">
-        <v>173703.214</v>
+        <v>154639.233</v>
       </c>
       <c r="E7">
-        <v>109614.508</v>
+        <v>96194.43799999999</v>
       </c>
       <c r="F7">
-        <v>104301</v>
+        <v>91294.07399999999</v>
       </c>
       <c r="G7">
-        <v>115015.353</v>
+        <v>101132.95</v>
+      </c>
+      <c r="H7">
+        <v>1528537283.841</v>
+      </c>
+      <c r="I7">
+        <v>1447530511.479</v>
+      </c>
+      <c r="J7">
+        <v>1610375299.537</v>
+      </c>
+      <c r="K7">
+        <v>12792887707.549</v>
+      </c>
+      <c r="L7">
+        <v>12143386037.83</v>
+      </c>
+      <c r="M7">
+        <v>13448785043.181</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>193590.894</v>
+        <v>172637.455</v>
       </c>
       <c r="C8">
-        <v>185341.823</v>
+        <v>164918.188</v>
       </c>
       <c r="D8">
-        <v>201864.932</v>
+        <v>180385.154</v>
       </c>
       <c r="E8">
-        <v>650563.9820000001</v>
+        <v>594505.8160000001</v>
       </c>
       <c r="F8">
-        <v>628286.041</v>
+        <v>573079.789</v>
       </c>
       <c r="G8">
-        <v>673019.3289999999</v>
+        <v>615998.8119999999</v>
+      </c>
+      <c r="H8">
+        <v>1528537283.841</v>
+      </c>
+      <c r="I8">
+        <v>1447530511.479</v>
+      </c>
+      <c r="J8">
+        <v>1610375299.537</v>
+      </c>
+      <c r="K8">
+        <v>79068848611.62498</v>
+      </c>
+      <c r="L8">
+        <v>76209860741.57201</v>
+      </c>
+      <c r="M8">
+        <v>81922199599.42</v>
       </c>
     </row>
   </sheetData>
